--- a/VerveStacks_IND_grids_kan60/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IND_grids_kan60/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan60\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{359D7971-04C6-421B-8532-32E7BE8DB617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B3E40F8-0A3B-49C6-8148-B8E591E706D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="12772" activeTab="1" xr2:uid="{765ADFFB-B043-48EE-88D7-E80CC497C08C}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{1ABDBB59-6A55-4375-8C3A-F4772C01653D}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2454,7 +2454,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{812EC8F8-ADEC-487B-BFF7-DE6F0FD76B6D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22BC2C45-C06B-401F-B416-3A96510A682A}">
   <dimension ref="B3:S217"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8057,7 +8057,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF4C83CC-F0C3-4A1B-B64B-730533AD8DFC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BCF2BE4-6070-4DD3-AB59-4BECAA29393B}">
   <dimension ref="B3:L49"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan60/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IND_grids_kan60/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan60\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B3E40F8-0A3B-49C6-8148-B8E591E706D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{760FE3EC-6BA3-459F-A13D-DCFE7E08ECDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{1ABDBB59-6A55-4375-8C3A-F4772C01653D}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12773" activeTab="1" xr2:uid="{F42B5312-2F11-489B-A740-B3842E138F64}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1711" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="690">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -672,7 +672,7 @@
     <t>grid link -394.0 km- way/201845280-765;way/293597835-765 (thermal x 0.7 N-1)</t>
   </si>
   <si>
-    <t>~commodity_geo</t>
+    <t>~commodity_geo:network=electricity</t>
   </si>
   <si>
     <t>commodity</t>
@@ -2104,6 +2104,9 @@
   </si>
   <si>
     <t>co2 pipeline -949 km- way/205942950-400 to ogci_10274.0</t>
+  </si>
+  <si>
+    <t>~commodity_geo:network=co2</t>
   </si>
 </sst>
 </file>
@@ -2454,7 +2457,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22BC2C45-C06B-401F-B416-3A96510A682A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D49DAF2-69ED-47BA-A11F-751AED99587B}">
   <dimension ref="B3:S217"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8057,19 +8060,22 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BCF2BE4-6070-4DD3-AB59-4BECAA29393B}">
-  <dimension ref="B3:L49"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ABE4499-1628-4B0D-8799-789222E813E9}">
+  <dimension ref="B3:S54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>0</v>
       </c>
       <c r="K3" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O3" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>1</v>
       </c>
@@ -8097,8 +8103,23 @@
       <c r="L4" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O4" t="s">
+        <v>212</v>
+      </c>
+      <c r="P4" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>214</v>
+      </c>
+      <c r="R4" t="s">
+        <v>215</v>
+      </c>
+      <c r="S4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>8</v>
       </c>
@@ -8126,8 +8147,20 @@
       <c r="L5" t="s">
         <v>644</v>
       </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O5" t="s">
+        <v>605</v>
+      </c>
+      <c r="P5" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q5">
+        <v>74.456786728891188</v>
+      </c>
+      <c r="R5">
+        <v>26.290069043638205</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>8</v>
       </c>
@@ -8155,8 +8188,20 @@
       <c r="L6" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O6" t="s">
+        <v>579</v>
+      </c>
+      <c r="P6" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q6">
+        <v>85.152159760446139</v>
+      </c>
+      <c r="R6">
+        <v>20.73642742592342</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>8</v>
       </c>
@@ -8184,8 +8229,20 @@
       <c r="L7" t="s">
         <v>646</v>
       </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O7" t="s">
+        <v>607</v>
+      </c>
+      <c r="P7" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q7">
+        <v>74.217962844113927</v>
+      </c>
+      <c r="R7">
+        <v>24.611083052454021</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>8</v>
       </c>
@@ -8213,8 +8270,20 @@
       <c r="L8" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O8" t="s">
+        <v>638</v>
+      </c>
+      <c r="P8" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q8">
+        <v>86.870433830061401</v>
+      </c>
+      <c r="R8">
+        <v>23.822446647165609</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>8</v>
       </c>
@@ -8242,8 +8311,20 @@
       <c r="L9" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O9" t="s">
+        <v>575</v>
+      </c>
+      <c r="P9" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q9">
+        <v>75.487884777440328</v>
+      </c>
+      <c r="R9">
+        <v>19.76889108398839</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>8</v>
       </c>
@@ -8271,8 +8352,20 @@
       <c r="L10" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O10" t="s">
+        <v>601</v>
+      </c>
+      <c r="P10" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q10">
+        <v>73.212244635036811</v>
+      </c>
+      <c r="R10">
+        <v>19.407791019327131</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -8300,8 +8393,20 @@
       <c r="L11" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O11" t="s">
+        <v>642</v>
+      </c>
+      <c r="P11" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q11">
+        <v>87.264675113645495</v>
+      </c>
+      <c r="R11">
+        <v>25.232329010566367</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>8</v>
       </c>
@@ -8329,8 +8434,20 @@
       <c r="L12" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O12" t="s">
+        <v>611</v>
+      </c>
+      <c r="P12" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12">
+        <v>88.540397678915653</v>
+      </c>
+      <c r="R12">
+        <v>23.017657471641133</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>8</v>
       </c>
@@ -8358,8 +8475,20 @@
       <c r="L13" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O13" t="s">
+        <v>587</v>
+      </c>
+      <c r="P13" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13">
+        <v>77.447273724409925</v>
+      </c>
+      <c r="R13">
+        <v>23.402301044116484</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>8</v>
       </c>
@@ -8387,8 +8516,20 @@
       <c r="L14" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O14" t="s">
+        <v>634</v>
+      </c>
+      <c r="P14" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14">
+        <v>85.509407607464126</v>
+      </c>
+      <c r="R14">
+        <v>25.162861135070283</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>8</v>
       </c>
@@ -8416,8 +8557,20 @@
       <c r="L15" t="s">
         <v>654</v>
       </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O15" t="s">
+        <v>640</v>
+      </c>
+      <c r="P15" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15">
+        <v>85.762897483004807</v>
+      </c>
+      <c r="R15">
+        <v>23.724123687245964</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>8</v>
       </c>
@@ -8445,8 +8598,20 @@
       <c r="L16" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O16" t="s">
+        <v>630</v>
+      </c>
+      <c r="P16" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16">
+        <v>90.372022567857883</v>
+      </c>
+      <c r="R16">
+        <v>26.45891349708441</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
         <v>8</v>
       </c>
@@ -8474,8 +8639,20 @@
       <c r="L17" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O17" t="s">
+        <v>615</v>
+      </c>
+      <c r="P17" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17">
+        <v>80.321224569041632</v>
+      </c>
+      <c r="R17">
+        <v>13.245992164940787</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
         <v>8</v>
       </c>
@@ -8503,8 +8680,20 @@
       <c r="L18" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O18" t="s">
+        <v>566</v>
+      </c>
+      <c r="P18" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18">
+        <v>78.799214450742014</v>
+      </c>
+      <c r="R18">
+        <v>14.382622741491918</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
         <v>8</v>
       </c>
@@ -8532,8 +8721,20 @@
       <c r="L19" t="s">
         <v>658</v>
       </c>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O19" t="s">
+        <v>595</v>
+      </c>
+      <c r="P19" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19">
+        <v>78.030826414577206</v>
+      </c>
+      <c r="R19">
+        <v>12.133113559842871</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
         <v>8</v>
       </c>
@@ -8561,8 +8762,20 @@
       <c r="L20" t="s">
         <v>659</v>
       </c>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O20" t="s">
+        <v>554</v>
+      </c>
+      <c r="P20" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20">
+        <v>78.256383334859336</v>
+      </c>
+      <c r="R20">
+        <v>24.217336068318083</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
         <v>8</v>
       </c>
@@ -8590,8 +8803,20 @@
       <c r="L21" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O21" t="s">
+        <v>561</v>
+      </c>
+      <c r="P21" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21">
+        <v>84.947765371961566</v>
+      </c>
+      <c r="R21">
+        <v>24.624691952501429</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
         <v>8</v>
       </c>
@@ -8619,8 +8844,20 @@
       <c r="L22" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O22" t="s">
+        <v>552</v>
+      </c>
+      <c r="P22" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22">
+        <v>78.226850078196293</v>
+      </c>
+      <c r="R22">
+        <v>26.113434002898089</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
         <v>8</v>
       </c>
@@ -8648,8 +8885,20 @@
       <c r="L23" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O23" t="s">
+        <v>564</v>
+      </c>
+      <c r="P23" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23">
+        <v>75.90401276433046</v>
+      </c>
+      <c r="R23">
+        <v>22.908338070793363</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
         <v>8</v>
       </c>
@@ -8677,8 +8926,20 @@
       <c r="L24" t="s">
         <v>663</v>
       </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O24" t="s">
+        <v>577</v>
+      </c>
+      <c r="P24" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24">
+        <v>79.766920149708255</v>
+      </c>
+      <c r="R24">
+        <v>23.13687497273823</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
         <v>8</v>
       </c>
@@ -8706,8 +8967,20 @@
       <c r="L25" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O25" t="s">
+        <v>589</v>
+      </c>
+      <c r="P25" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q25">
+        <v>75.665218786562164</v>
+      </c>
+      <c r="R25">
+        <v>26.651351516019087</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
         <v>8</v>
       </c>
@@ -8735,8 +9008,20 @@
       <c r="L26" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O26" t="s">
+        <v>622</v>
+      </c>
+      <c r="P26" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q26">
+        <v>75.139473514978192</v>
+      </c>
+      <c r="R26">
+        <v>32.76197127426434</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
         <v>8</v>
       </c>
@@ -8764,8 +9049,20 @@
       <c r="L27" t="s">
         <v>666</v>
       </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O27" t="s">
+        <v>585</v>
+      </c>
+      <c r="P27" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q27">
+        <v>83.981445987100173</v>
+      </c>
+      <c r="R27">
+        <v>22.092499489995411</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
         <v>8</v>
       </c>
@@ -8793,8 +9090,20 @@
       <c r="L28" t="s">
         <v>667</v>
       </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O28" t="s">
+        <v>597</v>
+      </c>
+      <c r="P28" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q28">
+        <v>82.054666595428074</v>
+      </c>
+      <c r="R28">
+        <v>17.091828850387046</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
         <v>8</v>
       </c>
@@ -8822,8 +9131,20 @@
       <c r="L29" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O29" t="s">
+        <v>632</v>
+      </c>
+      <c r="P29" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29">
+        <v>92.721473704265804</v>
+      </c>
+      <c r="R29">
+        <v>24.82739009961811</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
         <v>8</v>
       </c>
@@ -8851,8 +9172,20 @@
       <c r="L30" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O30" t="s">
+        <v>583</v>
+      </c>
+      <c r="P30" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q30">
+        <v>82.762172184031854</v>
+      </c>
+      <c r="R30">
+        <v>22.271692751270525</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
         <v>8</v>
       </c>
@@ -8880,8 +9213,20 @@
       <c r="L31" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O31" t="s">
+        <v>573</v>
+      </c>
+      <c r="P31" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q31">
+        <v>78.177770343689502</v>
+      </c>
+      <c r="R31">
+        <v>15.673490343021944</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
         <v>8</v>
       </c>
@@ -8909,8 +9254,20 @@
       <c r="L32" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O32" t="s">
+        <v>626</v>
+      </c>
+      <c r="P32" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32">
+        <v>77.897253599999999</v>
+      </c>
+      <c r="R32">
+        <v>9.8765525802110581</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
         <v>8</v>
       </c>
@@ -8938,8 +9295,20 @@
       <c r="L33" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O33" t="s">
+        <v>609</v>
+      </c>
+      <c r="P33" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q33">
+        <v>78.933015166346195</v>
+      </c>
+      <c r="R33">
+        <v>27.219511183229635</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
         <v>8</v>
       </c>
@@ -8967,8 +9336,20 @@
       <c r="L34" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O34" t="s">
+        <v>548</v>
+      </c>
+      <c r="P34" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q34">
+        <v>77.72084125829474</v>
+      </c>
+      <c r="R34">
+        <v>29.133730586510051</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
         <v>8</v>
       </c>
@@ -8996,8 +9377,20 @@
       <c r="L35" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O35" t="s">
+        <v>591</v>
+      </c>
+      <c r="P35" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q35">
+        <v>75.146078508432495</v>
+      </c>
+      <c r="R35">
+        <v>30.784075715982738</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
         <v>8</v>
       </c>
@@ -9025,8 +9418,20 @@
       <c r="L36" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O36" t="s">
+        <v>617</v>
+      </c>
+      <c r="P36" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q36">
+        <v>69.157237957718323</v>
+      </c>
+      <c r="R36">
+        <v>23.363341779801441</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
         <v>8</v>
       </c>
@@ -9054,8 +9459,20 @@
       <c r="L37" t="s">
         <v>676</v>
       </c>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O37" t="s">
+        <v>613</v>
+      </c>
+      <c r="P37" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q37">
+        <v>79.946544614576553</v>
+      </c>
+      <c r="R37">
+        <v>16.215360307270966</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
         <v>8</v>
       </c>
@@ -9083,8 +9500,20 @@
       <c r="L38" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O38" t="s">
+        <v>620</v>
+      </c>
+      <c r="P38" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q38">
+        <v>72.481935936664442</v>
+      </c>
+      <c r="R38">
+        <v>27.5115253825116</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
         <v>8</v>
       </c>
@@ -9112,8 +9541,20 @@
       <c r="L39" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O39" t="s">
+        <v>593</v>
+      </c>
+      <c r="P39" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q39">
+        <v>77.286369742888553</v>
+      </c>
+      <c r="R39">
+        <v>16.201102167631014</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
         <v>8</v>
       </c>
@@ -9141,8 +9582,20 @@
       <c r="L40" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O40" t="s">
+        <v>571</v>
+      </c>
+      <c r="P40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q40">
+        <v>81.351217595566879</v>
+      </c>
+      <c r="R40">
+        <v>21.371862928755149</v>
+      </c>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
         <v>8</v>
       </c>
@@ -9170,8 +9623,20 @@
       <c r="L41" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O41" t="s">
+        <v>636</v>
+      </c>
+      <c r="P41" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q41">
+        <v>83.708038953953974</v>
+      </c>
+      <c r="R41">
+        <v>25.128271214974891</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
         <v>8</v>
       </c>
@@ -9199,8 +9664,20 @@
       <c r="L42" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O42" t="s">
+        <v>557</v>
+      </c>
+      <c r="P42" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q42">
+        <v>80.712672268626605</v>
+      </c>
+      <c r="R42">
+        <v>24.573636093214287</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
         <v>8</v>
       </c>
@@ -9228,8 +9705,20 @@
       <c r="L43" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O43" t="s">
+        <v>599</v>
+      </c>
+      <c r="P43" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q43">
+        <v>77.697852005819513</v>
+      </c>
+      <c r="R43">
+        <v>28.196007553336685</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
         <v>8</v>
       </c>
@@ -9257,8 +9746,20 @@
       <c r="L44" t="s">
         <v>683</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O44" t="s">
+        <v>603</v>
+      </c>
+      <c r="P44" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q44">
+        <v>82.575591981645132</v>
+      </c>
+      <c r="R44">
+        <v>23.949462146407761</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
         <v>8</v>
       </c>
@@ -9286,8 +9787,20 @@
       <c r="L45" t="s">
         <v>684</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O45" t="s">
+        <v>569</v>
+      </c>
+      <c r="P45" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45">
+        <v>76.051201531523105</v>
+      </c>
+      <c r="R45">
+        <v>17.607760270934016</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
         <v>8</v>
       </c>
@@ -9315,8 +9828,20 @@
       <c r="L46" t="s">
         <v>685</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O46" t="s">
+        <v>624</v>
+      </c>
+      <c r="P46" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q46">
+        <v>84.99678729999998</v>
+      </c>
+      <c r="R46">
+        <v>20.789433971597354</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
         <v>8</v>
       </c>
@@ -9344,8 +9869,20 @@
       <c r="L47" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O47" t="s">
+        <v>628</v>
+      </c>
+      <c r="P47" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47">
+        <v>92.769229427644319</v>
+      </c>
+      <c r="R47">
+        <v>26.874103883267651</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
         <v>8</v>
       </c>
@@ -9373,8 +9910,20 @@
       <c r="L48" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O48" t="s">
+        <v>581</v>
+      </c>
+      <c r="P48" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q48">
+        <v>73.377135632267908</v>
+      </c>
+      <c r="R48">
+        <v>22.317293030637487</v>
+      </c>
+    </row>
+    <row r="49" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
         <v>8</v>
       </c>
@@ -9401,6 +9950,88 @@
       </c>
       <c r="L49" t="s">
         <v>688</v>
+      </c>
+      <c r="O49" t="s">
+        <v>559</v>
+      </c>
+      <c r="P49" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q49">
+        <v>78.492722981662908</v>
+      </c>
+      <c r="R49">
+        <v>20.669102672493342</v>
+      </c>
+    </row>
+    <row r="50" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O50" t="s">
+        <v>562</v>
+      </c>
+      <c r="P50" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q50">
+        <v>94.964444439999994</v>
+      </c>
+      <c r="R50">
+        <v>26.889166670000002</v>
+      </c>
+    </row>
+    <row r="51" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O51" t="s">
+        <v>618</v>
+      </c>
+      <c r="P51" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q51">
+        <v>71.816666670000004</v>
+      </c>
+      <c r="R51">
+        <v>25.258888890000001</v>
+      </c>
+    </row>
+    <row r="52" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O52" t="s">
+        <v>549</v>
+      </c>
+      <c r="P52" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q52">
+        <v>71.819444439999998</v>
+      </c>
+      <c r="R52">
+        <v>25.258888890000001</v>
+      </c>
+    </row>
+    <row r="53" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O53" t="s">
+        <v>555</v>
+      </c>
+      <c r="P53" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q53">
+        <v>72.902777779999994</v>
+      </c>
+      <c r="R53">
+        <v>22.477499999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O54" t="s">
+        <v>567</v>
+      </c>
+      <c r="P54" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q54">
+        <v>71.624166669999994</v>
+      </c>
+      <c r="R54">
+        <v>18.228611109999999</v>
       </c>
     </row>
   </sheetData>
